--- a/public/docs/Template_Cutting.xlsx
+++ b/public/docs/Template_Cutting.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
   <si>
     <t>Type</t>
   </si>
@@ -174,6 +174,39 @@
   </si>
   <si>
     <t>Memory Twist</t>
+  </si>
+  <si>
+    <t>QRCode EJ-A</t>
+  </si>
+  <si>
+    <t>QRCode EJ-B</t>
+  </si>
+  <si>
+    <t>CCT Code 2</t>
+  </si>
+  <si>
+    <t>CCT No. 2</t>
+  </si>
+  <si>
+    <t>Cust No. 2</t>
+  </si>
+  <si>
+    <t>Kind 2</t>
+  </si>
+  <si>
+    <t>Size 2</t>
+  </si>
+  <si>
+    <t>Col 2</t>
+  </si>
+  <si>
+    <t>C/L 2</t>
+  </si>
+  <si>
+    <t>Barcode Mesin 2</t>
+  </si>
+  <si>
+    <t>QRCode Mesin</t>
   </si>
   <si>
     <t>ASSY-001</t>
@@ -573,7 +606,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BD1"/>
+  <dimension ref="A1:BO1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -629,12 +662,23 @@
     <col min="51" max="51" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="52" max="52" width="6.856" bestFit="true" customWidth="true" style="0"/>
     <col min="53" max="53" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="54" max="54" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="55" max="55" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="56" max="56" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="54" max="54" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="55" max="55" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="56" max="56" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="57" max="57" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="58" max="58" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="59" max="59" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="60" max="60" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="61" max="61" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="62" max="62" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="63" max="63" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="64" max="64" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="65" max="65" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="66" max="66" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="67" max="67" width="12.854" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:67">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,14 +838,47 @@
       <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
